--- a/Data/Happy Town Expense.xlsx
+++ b/Data/Happy Town Expense.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d772b42a7a1256b2/Desktop/Business/TSK Constructions/Projects/Building Construction/Happy Town - Sulur/Accounts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="497" documentId="13_ncr:1_{DE40AB4E-5E7E-4BE7-A52F-372CFBFF2560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{350F849B-F7A3-4E2C-83DD-49B6B11C3CFB}"/>
+  <xr:revisionPtr revIDLastSave="506" documentId="13_ncr:1_{DE40AB4E-5E7E-4BE7-A52F-372CFBFF2560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C10F29E8-A23D-4638-AFA5-20F01781A108}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId6"/>
+    <pivotCache cacheId="7" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1003" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="341">
   <si>
     <t>DATE</t>
   </si>
@@ -4098,7 +4098,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{25AC62C7-A7F3-4225-A13E-8201E9F5861E}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Expense">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{25AC62C7-A7F3-4225-A13E-8201E9F5861E}" name="PivotTable1" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Expense">
   <location ref="D3:E7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField showAll="0"/>
@@ -4200,7 +4200,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1FC8C9A3-14B4-46FA-8D51-AAF7A0B6E9CA}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Expense">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1FC8C9A3-14B4-46FA-8D51-AAF7A0B6E9CA}" name="PivotTable4" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Expense">
   <location ref="A3:B29" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField showAll="0"/>
@@ -4368,7 +4368,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F4F3CF52-2B38-440E-A2E0-E3EBDEB38030}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Expense">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F4F3CF52-2B38-440E-A2E0-E3EBDEB38030}" name="PivotTable3" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Expense">
   <location ref="J3:K6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField showAll="0"/>
@@ -4467,7 +4467,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{123E7EF1-D634-4326-8B1F-206D3919FDCB}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Expense">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{123E7EF1-D634-4326-8B1F-206D3919FDCB}" name="PivotTable2" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Expense">
   <location ref="G3:H8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField showAll="0"/>
@@ -5417,7 +5417,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E716AC5E-A74E-4151-8738-1C2F14C945B6}">
-  <dimension ref="A1:L416"/>
+  <dimension ref="A1:L418"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.08984375" style="5" bestFit="1" customWidth="1"/>
@@ -5473,7 +5473,7 @@
       </c>
       <c r="J2" s="7">
         <f>SUM(C2:C510)</f>
-        <v>4348987</v>
+        <v>4375987</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
@@ -5494,7 +5494,7 @@
       </c>
       <c r="J3" s="7">
         <f>J1-J2</f>
-        <v>-19787</v>
+        <v>-46787</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
@@ -11292,17 +11292,45 @@
       </c>
     </row>
     <row r="416" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A416" s="5">
+      <c r="A416" s="4">
         <v>46144</v>
       </c>
-      <c r="B416" s="28" t="s">
+      <c r="B416" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C416" s="8">
+      <c r="C416" s="7">
         <v>20000</v>
       </c>
-      <c r="D416" s="28" t="s">
+      <c r="D416" s="1" t="s">
         <v>335</v>
+      </c>
+    </row>
+    <row r="417" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A417" s="4">
+        <v>46154</v>
+      </c>
+      <c r="B417" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="C417" s="7">
+        <v>2000</v>
+      </c>
+      <c r="D417" s="1" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="418" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A418" s="5">
+        <v>46172</v>
+      </c>
+      <c r="B418" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="C418" s="8">
+        <v>25000</v>
+      </c>
+      <c r="D418" s="28" t="s">
+        <v>179</v>
       </c>
     </row>
   </sheetData>
